--- a/reports/一级子公司A_现金流量表_2026-04.xlsx
+++ b/reports/一级子公司A_现金流量表_2026-04.xlsx
@@ -1996,10 +1996,10 @@
         </is>
       </c>
       <c r="F4" s="15" t="n">
-        <v>152646000</v>
+        <v>149801884</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>573948960</v>
+        <v>565503769</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2030,10 +2030,10 @@
         </is>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0</v>
+        <v>3008182</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0</v>
+        <v>11280045</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2063,10 +2063,10 @@
         </is>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0</v>
+        <v>1492639</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0</v>
+        <v>5619066</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2096,10 +2096,10 @@
         </is>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0</v>
+        <v>750255</v>
       </c>
       <c r="G7" s="15" t="n">
-        <v>0</v>
+        <v>2822251</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2129,10 +2129,10 @@
         </is>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0</v>
+        <v>598817</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0</v>
+        <v>2246899</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2162,10 +2162,10 @@
         </is>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0</v>
+        <v>448723</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0</v>
+        <v>1693042</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2195,10 +2195,10 @@
         </is>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0</v>
+        <v>300334</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0</v>
+        <v>1124203</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2228,10 +2228,10 @@
         </is>
       </c>
       <c r="F11" s="15" t="n">
-        <v>0</v>
+        <v>223760</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0</v>
+        <v>845604</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
@@ -2261,10 +2261,10 @@
         </is>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0</v>
+        <v>150465</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0</v>
+        <v>562885</v>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
@@ -2294,10 +2294,10 @@
         </is>
       </c>
       <c r="F13" s="15" t="n">
-        <v>0</v>
+        <v>372528</v>
       </c>
       <c r="G13" s="15" t="n">
-        <v>0</v>
+        <v>1407160</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
@@ -2327,10 +2327,10 @@
         </is>
       </c>
       <c r="F14" s="15" t="n">
-        <v>0</v>
+        <v>189058</v>
       </c>
       <c r="G14" s="15" t="n">
-        <v>0</v>
+        <v>708307</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2360,10 +2360,10 @@
         </is>
       </c>
       <c r="F15" s="15" t="n">
-        <v>0</v>
+        <v>118558</v>
       </c>
       <c r="G15" s="15" t="n">
-        <v>0</v>
+        <v>446786</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2393,10 +2393,10 @@
         </is>
       </c>
       <c r="F16" s="15" t="n">
-        <v>391400</v>
+        <v>387118</v>
       </c>
       <c r="G16" s="15" t="n">
-        <v>1471664</v>
+        <v>1454605</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2426,10 +2426,10 @@
         </is>
       </c>
       <c r="F17" s="15" t="n">
-        <v>2781000</v>
+        <v>2741034</v>
       </c>
       <c r="G17" s="15" t="n">
-        <v>10456560</v>
+        <v>10295993</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2546,7 +2546,7 @@
         </is>
       </c>
       <c r="F21" s="20" t="n">
-        <v>155818400</v>
+        <v>160583355</v>
       </c>
       <c r="G21" s="20" t="n"/>
     </row>
@@ -2577,10 +2577,10 @@
         </is>
       </c>
       <c r="F22" s="15" t="n">
-        <v>98880000</v>
+        <v>97026474</v>
       </c>
       <c r="G22" s="15" t="n">
-        <v>371788800</v>
+        <v>366643594</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2610,10 +2610,10 @@
         </is>
       </c>
       <c r="F23" s="15" t="n">
-        <v>0</v>
+        <v>1003374</v>
       </c>
       <c r="G23" s="15" t="n">
-        <v>0</v>
+        <v>3756497</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2643,10 +2643,10 @@
         </is>
       </c>
       <c r="F24" s="15" t="n">
-        <v>0</v>
+        <v>745365</v>
       </c>
       <c r="G24" s="15" t="n">
-        <v>0</v>
+        <v>2811579</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2676,10 +2676,10 @@
         </is>
       </c>
       <c r="F25" s="15" t="n">
-        <v>0</v>
+        <v>501053</v>
       </c>
       <c r="G25" s="15" t="n">
-        <v>0</v>
+        <v>1880675</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
@@ -2709,10 +2709,10 @@
         </is>
       </c>
       <c r="F26" s="15" t="n">
-        <v>0</v>
+        <v>373484</v>
       </c>
       <c r="G26" s="15" t="n">
-        <v>0</v>
+        <v>1404466</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
@@ -2742,10 +2742,10 @@
         </is>
       </c>
       <c r="F27" s="15" t="n">
-        <v>0</v>
+        <v>249832</v>
       </c>
       <c r="G27" s="15" t="n">
-        <v>0</v>
+        <v>940801</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2775,10 +2775,10 @@
         </is>
       </c>
       <c r="F28" s="15" t="n">
-        <v>0</v>
+        <v>188289</v>
       </c>
       <c r="G28" s="15" t="n">
-        <v>0</v>
+        <v>705837</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2808,10 +2808,10 @@
         </is>
       </c>
       <c r="F29" s="15" t="n">
-        <v>16171000</v>
+        <v>15919396</v>
       </c>
       <c r="G29" s="15" t="n">
-        <v>60802960</v>
+        <v>60107663</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2841,10 +2841,10 @@
         </is>
       </c>
       <c r="F30" s="15" t="n">
-        <v>8240000</v>
+        <v>8154788</v>
       </c>
       <c r="G30" s="15" t="n">
-        <v>30982400</v>
+        <v>30511916</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="F31" s="15" t="n">
-        <v>3399000</v>
+        <v>3338963</v>
       </c>
       <c r="G31" s="15" t="n">
-        <v>12780240</v>
+        <v>12619209</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2936,7 +2936,7 @@
         </is>
       </c>
       <c r="F33" s="20" t="n">
-        <v>126690000</v>
+        <v>127501018</v>
       </c>
       <c r="G33" s="20" t="n"/>
     </row>
@@ -2967,7 +2967,7 @@
         </is>
       </c>
       <c r="F34" s="20" t="n">
-        <v>29128400</v>
+        <v>33082337</v>
       </c>
       <c r="G34" s="20" t="n"/>
     </row>
@@ -3093,10 +3093,10 @@
         </is>
       </c>
       <c r="F38" s="15" t="n">
-        <v>185400</v>
+        <v>182779</v>
       </c>
       <c r="G38" s="15" t="n">
-        <v>741600</v>
+        <v>733686</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3159,10 +3159,10 @@
         </is>
       </c>
       <c r="F40" s="15" t="n">
-        <v>1545000</v>
+        <v>1518061</v>
       </c>
       <c r="G40" s="15" t="n">
-        <v>6180000</v>
+        <v>6104179</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3192,10 +3192,10 @@
         </is>
       </c>
       <c r="F41" s="15" t="n">
-        <v>947600</v>
+        <v>939388</v>
       </c>
       <c r="G41" s="15" t="n">
-        <v>3790400</v>
+        <v>3737683</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3225,7 +3225,7 @@
         </is>
       </c>
       <c r="F42" s="20" t="n">
-        <v>1730400</v>
+        <v>1700840</v>
       </c>
       <c r="G42" s="20" t="n"/>
     </row>
@@ -3256,10 +3256,10 @@
         </is>
       </c>
       <c r="F43" s="15" t="n">
-        <v>14420000</v>
+        <v>14247793</v>
       </c>
       <c r="G43" s="15" t="n">
-        <v>57680000</v>
+        <v>56773099</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3289,10 +3289,10 @@
         </is>
       </c>
       <c r="F44" s="15" t="n">
-        <v>2060000</v>
+        <v>2015774</v>
       </c>
       <c r="G44" s="15" t="n">
-        <v>8240000</v>
+        <v>8082985</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3322,10 +3322,10 @@
         </is>
       </c>
       <c r="F45" s="15" t="n">
-        <v>10300000</v>
+        <v>10164613</v>
       </c>
       <c r="G45" s="15" t="n">
-        <v>41200000</v>
+        <v>40625570</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3454,10 +3454,10 @@
         </is>
       </c>
       <c r="F49" s="15" t="n">
-        <v>391400</v>
+        <v>384794</v>
       </c>
       <c r="G49" s="15" t="n">
-        <v>1565600</v>
+        <v>1546705</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3487,7 +3487,7 @@
         </is>
       </c>
       <c r="F50" s="20" t="n">
-        <v>14811400</v>
+        <v>14632587</v>
       </c>
       <c r="G50" s="20" t="n"/>
     </row>
@@ -3518,7 +3518,7 @@
         </is>
       </c>
       <c r="F51" s="20" t="n">
-        <v>-13081000</v>
+        <v>-12931747</v>
       </c>
       <c r="G51" s="20" t="n"/>
     </row>
@@ -3578,10 +3578,10 @@
         </is>
       </c>
       <c r="F53" s="15" t="n">
-        <v>3605000</v>
+        <v>3543628</v>
       </c>
       <c r="G53" s="15" t="n">
-        <v>14420000</v>
+        <v>14223338</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3644,10 +3644,10 @@
         </is>
       </c>
       <c r="F55" s="15" t="n">
-        <v>5665000</v>
+        <v>5576163</v>
       </c>
       <c r="G55" s="15" t="n">
-        <v>22660000</v>
+        <v>22310152</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3677,10 +3677,10 @@
         </is>
       </c>
       <c r="F56" s="15" t="n">
-        <v>5665000</v>
+        <v>5595364</v>
       </c>
       <c r="G56" s="15" t="n">
-        <v>22660000</v>
+        <v>22414381</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="F57" s="15" t="n">
-        <v>185400</v>
+        <v>183121</v>
       </c>
       <c r="G57" s="15" t="n">
-        <v>741600</v>
+        <v>730259</v>
       </c>
     </row>
     <row r="58" ht="18" customHeight="1">
@@ -3743,7 +3743,7 @@
         </is>
       </c>
       <c r="F58" s="20" t="n">
-        <v>9455400</v>
+        <v>9302912</v>
       </c>
       <c r="G58" s="20" t="n"/>
     </row>
@@ -3774,10 +3774,10 @@
         </is>
       </c>
       <c r="F59" s="15" t="n">
-        <v>4635000</v>
+        <v>4591107</v>
       </c>
       <c r="G59" s="15" t="n">
-        <v>18540000</v>
+        <v>18271411</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3807,10 +3807,10 @@
         </is>
       </c>
       <c r="F60" s="15" t="n">
-        <v>4635000</v>
+        <v>4554552</v>
       </c>
       <c r="G60" s="15" t="n">
-        <v>18540000</v>
+        <v>18316121</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3840,10 +3840,10 @@
         </is>
       </c>
       <c r="F61" s="15" t="n">
-        <v>741600</v>
+        <v>735624</v>
       </c>
       <c r="G61" s="15" t="n">
-        <v>2966400</v>
+        <v>2927685</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3902,10 +3902,10 @@
         </is>
       </c>
       <c r="F63" s="15" t="n">
-        <v>648900</v>
+        <v>643296</v>
       </c>
       <c r="G63" s="15" t="n">
-        <v>2595600</v>
+        <v>2565564</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -3935,10 +3935,10 @@
         </is>
       </c>
       <c r="F64" s="15" t="n">
-        <v>92700</v>
+        <v>91193</v>
       </c>
       <c r="G64" s="15" t="n">
-        <v>370800</v>
+        <v>365283</v>
       </c>
     </row>
     <row r="65" ht="18" customHeight="1">
@@ -3968,7 +3968,7 @@
         </is>
       </c>
       <c r="F65" s="20" t="n">
-        <v>5469300</v>
+        <v>5417924</v>
       </c>
       <c r="G65" s="20" t="n"/>
     </row>
@@ -3999,7 +3999,7 @@
         </is>
       </c>
       <c r="F66" s="20" t="n">
-        <v>3986100</v>
+        <v>3884988</v>
       </c>
       <c r="G66" s="20" t="n"/>
     </row>
@@ -4059,7 +4059,7 @@
         </is>
       </c>
       <c r="F68" s="20" t="n">
-        <v>20033500</v>
+        <v>24035578</v>
       </c>
       <c r="G68" s="20" t="n"/>
     </row>
@@ -4119,7 +4119,7 @@
         </is>
       </c>
       <c r="F70" s="26" t="n">
-        <v>20033500</v>
+        <v>24035578</v>
       </c>
       <c r="G70" s="26" t="n"/>
     </row>
